--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.7.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.2; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.2; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.3; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.3; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.4; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.4; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.1; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.11.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>

--- a/scripts/build/into_golden.xlsx
+++ b/scripts/build/into_golden.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="Rate">0.2</definedName>
-    <definedName name="Frazaro.Build">"Frazaro 0.11.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.12.0; into sha256:79DAD00796744AEA14D841A3B0395670AB87161A447A084EAE7CA20708208C85 with 2 cell formats and metadata 1; sentences sha256:14D649F19C7F73A7F4DC6F863744AAB6E09E3DC56DA6CEC91DB9E7D52CCFE451 over 301 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" calcId="191029"/>
 </workbook>
